--- a/branches/ci/gh-pages-preview/StructureDefinition-mii-pr-kardio-linksventrikulaere-ejektionsfraktion.xlsx
+++ b/branches/ci/gh-pages-preview/StructureDefinition-mii-pr-kardio-linksventrikulaere-ejektionsfraktion.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$144</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$106</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5552" uniqueCount="667">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4099" uniqueCount="610">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2027.0.0-ballot.rc1</t>
+    <t>2027.0.0-ballot</t>
   </si>
   <si>
     <t>Name</t>
@@ -81,7 +81,7 @@
     <t>Jurisdiction</t>
   </si>
   <si>
-    <t>Unknown region code '276'</t>
+    <t>Germany</t>
   </si>
   <si>
     <t>Description</t>
@@ -1737,52 +1737,12 @@
     <t>Observation.referenceRange:normal.low</t>
   </si>
   <si>
-    <t>Observation.referenceRange:normal.low.id</t>
-  </si>
-  <si>
-    <t>Observation.referenceRange.low.id</t>
-  </si>
-  <si>
-    <t>Observation.referenceRange:normal.low.extension</t>
-  </si>
-  <si>
-    <t>Observation.referenceRange.low.extension</t>
-  </si>
-  <si>
-    <t>Observation.referenceRange:normal.low.value</t>
-  </si>
-  <si>
-    <t>Observation.referenceRange.low.value</t>
-  </si>
-  <si>
-    <t>50</t>
-  </si>
-  <si>
-    <t>Observation.referenceRange:normal.low.comparator</t>
-  </si>
-  <si>
-    <t>Observation.referenceRange.low.comparator</t>
-  </si>
-  <si>
-    <t>Not allowed to be used in this context</t>
-  </si>
-  <si>
-    <t>Observation.referenceRange:normal.low.unit</t>
-  </si>
-  <si>
-    <t>Observation.referenceRange.low.unit</t>
-  </si>
-  <si>
-    <t>Observation.referenceRange:normal.low.system</t>
-  </si>
-  <si>
-    <t>Observation.referenceRange.low.system</t>
-  </si>
-  <si>
-    <t>Observation.referenceRange:normal.low.code</t>
-  </si>
-  <si>
-    <t>Observation.referenceRange.low.code</t>
+    <t>&lt;valueQuantity xmlns="http://hl7.org/fhir"&gt;
+  &lt;value value="50"/&gt;
+  &lt;unit value="%"/&gt;
+  &lt;system value="http://unitsofmeasure.org"/&gt;
+  &lt;code value="%"/&gt;
+&lt;/valueQuantity&gt;</t>
   </si>
   <si>
     <t>Observation.referenceRange:normal.high</t>
@@ -1803,111 +1763,6 @@
     <t>Normal</t>
   </si>
   <si>
-    <t>Observation.referenceRange:mild</t>
-  </si>
-  <si>
-    <t>mild</t>
-  </si>
-  <si>
-    <t>Observation.referenceRange:mild.id</t>
-  </si>
-  <si>
-    <t>Observation.referenceRange:mild.extension</t>
-  </si>
-  <si>
-    <t>Observation.referenceRange:mild.modifierExtension</t>
-  </si>
-  <si>
-    <t>Observation.referenceRange:mild.low</t>
-  </si>
-  <si>
-    <t>Observation.referenceRange:mild.low.id</t>
-  </si>
-  <si>
-    <t>Observation.referenceRange:mild.low.extension</t>
-  </si>
-  <si>
-    <t>Observation.referenceRange:mild.low.value</t>
-  </si>
-  <si>
-    <t>41</t>
-  </si>
-  <si>
-    <t>Observation.referenceRange:mild.low.comparator</t>
-  </si>
-  <si>
-    <t>Observation.referenceRange:mild.low.unit</t>
-  </si>
-  <si>
-    <t>Observation.referenceRange:mild.low.system</t>
-  </si>
-  <si>
-    <t>Observation.referenceRange:mild.low.code</t>
-  </si>
-  <si>
-    <t>Observation.referenceRange:mild.high</t>
-  </si>
-  <si>
-    <t>Observation.referenceRange:mild.high.id</t>
-  </si>
-  <si>
-    <t>Observation.referenceRange.high.id</t>
-  </si>
-  <si>
-    <t>Observation.referenceRange:mild.high.extension</t>
-  </si>
-  <si>
-    <t>Observation.referenceRange.high.extension</t>
-  </si>
-  <si>
-    <t>Observation.referenceRange:mild.high.value</t>
-  </si>
-  <si>
-    <t>Observation.referenceRange.high.value</t>
-  </si>
-  <si>
-    <t>49</t>
-  </si>
-  <si>
-    <t>Observation.referenceRange:mild.high.comparator</t>
-  </si>
-  <si>
-    <t>Observation.referenceRange.high.comparator</t>
-  </si>
-  <si>
-    <t>Observation.referenceRange:mild.high.unit</t>
-  </si>
-  <si>
-    <t>Observation.referenceRange.high.unit</t>
-  </si>
-  <si>
-    <t>Observation.referenceRange:mild.high.system</t>
-  </si>
-  <si>
-    <t>Observation.referenceRange.high.system</t>
-  </si>
-  <si>
-    <t>Observation.referenceRange:mild.high.code</t>
-  </si>
-  <si>
-    <t>Observation.referenceRange.high.code</t>
-  </si>
-  <si>
-    <t>Observation.referenceRange:mild.type</t>
-  </si>
-  <si>
-    <t>Observation.referenceRange:mild.appliesTo</t>
-  </si>
-  <si>
-    <t>Observation.referenceRange:mild.age</t>
-  </si>
-  <si>
-    <t>Observation.referenceRange:mild.text</t>
-  </si>
-  <si>
-    <t>Mildly reduced</t>
-  </si>
-  <si>
     <t>Observation.referenceRange:reduced</t>
   </si>
   <si>
@@ -1929,28 +1784,12 @@
     <t>Observation.referenceRange:reduced.high</t>
   </si>
   <si>
-    <t>Observation.referenceRange:reduced.high.id</t>
-  </si>
-  <si>
-    <t>Observation.referenceRange:reduced.high.extension</t>
-  </si>
-  <si>
-    <t>Observation.referenceRange:reduced.high.value</t>
-  </si>
-  <si>
-    <t>40</t>
-  </si>
-  <si>
-    <t>Observation.referenceRange:reduced.high.comparator</t>
-  </si>
-  <si>
-    <t>Observation.referenceRange:reduced.high.unit</t>
-  </si>
-  <si>
-    <t>Observation.referenceRange:reduced.high.system</t>
-  </si>
-  <si>
-    <t>Observation.referenceRange:reduced.high.code</t>
+    <t>&lt;valueQuantity xmlns="http://hl7.org/fhir"&gt;
+  &lt;value value="49"/&gt;
+  &lt;unit value="%"/&gt;
+  &lt;system value="http://unitsofmeasure.org"/&gt;
+  &lt;code value="%"/&gt;
+&lt;/valueQuantity&gt;</t>
   </si>
   <si>
     <t>Observation.referenceRange:reduced.type</t>
@@ -2412,7 +2251,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AP144"/>
+  <dimension ref="A1:AP106"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="45.265625" customWidth="true" bestFit="true"/>
@@ -12038,7 +11877,7 @@
         <v>82</v>
       </c>
       <c r="S80" t="s" s="2">
-        <v>82</v>
+        <v>549</v>
       </c>
       <c r="T80" t="s" s="2">
         <v>82</v>
@@ -12112,10 +11951,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>550</v>
+        <v>513</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -12138,13 +11977,13 @@
         <v>82</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>222</v>
+        <v>507</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>223</v>
+        <v>514</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>224</v>
+        <v>515</v>
       </c>
       <c r="N81" s="2"/>
       <c r="O81" s="2"/>
@@ -12195,7 +12034,7 @@
         <v>82</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>225</v>
+        <v>513</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>80</v>
@@ -12204,10 +12043,10 @@
         <v>93</v>
       </c>
       <c r="AI81" t="s" s="2">
-        <v>82</v>
+        <v>510</v>
       </c>
       <c r="AJ81" t="s" s="2">
-        <v>82</v>
+        <v>105</v>
       </c>
       <c r="AK81" t="s" s="2">
         <v>82</v>
@@ -12216,10 +12055,10 @@
         <v>82</v>
       </c>
       <c r="AM81" t="s" s="2">
-        <v>82</v>
+        <v>511</v>
       </c>
       <c r="AN81" t="s" s="2">
-        <v>226</v>
+        <v>516</v>
       </c>
       <c r="AO81" t="s" s="2">
         <v>82</v>
@@ -12233,18 +12072,18 @@
         <v>551</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>552</v>
+        <v>517</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
-        <v>138</v>
+        <v>82</v>
       </c>
       <c r="E82" s="2"/>
       <c r="F82" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G82" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H82" t="s" s="2">
         <v>82</v>
@@ -12256,18 +12095,20 @@
         <v>82</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>139</v>
+        <v>191</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>140</v>
+        <v>518</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>228</v>
+        <v>519</v>
       </c>
       <c r="N82" t="s" s="2">
-        <v>142</v>
-      </c>
-      <c r="O82" s="2"/>
+        <v>520</v>
+      </c>
+      <c r="O82" t="s" s="2">
+        <v>521</v>
+      </c>
       <c r="P82" t="s" s="2">
         <v>82</v>
       </c>
@@ -12291,55 +12132,55 @@
         <v>82</v>
       </c>
       <c r="X82" t="s" s="2">
-        <v>82</v>
+        <v>117</v>
       </c>
       <c r="Y82" t="s" s="2">
-        <v>82</v>
+        <v>522</v>
       </c>
       <c r="Z82" t="s" s="2">
-        <v>82</v>
+        <v>523</v>
       </c>
       <c r="AA82" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AB82" t="s" s="2">
-        <v>229</v>
+        <v>82</v>
       </c>
       <c r="AC82" t="s" s="2">
-        <v>230</v>
+        <v>82</v>
       </c>
       <c r="AD82" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE82" t="s" s="2">
-        <v>199</v>
+        <v>82</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>231</v>
+        <v>517</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH82" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI82" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ82" t="s" s="2">
-        <v>144</v>
+        <v>105</v>
       </c>
       <c r="AK82" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL82" t="s" s="2">
-        <v>82</v>
+        <v>524</v>
       </c>
       <c r="AM82" t="s" s="2">
-        <v>82</v>
+        <v>525</v>
       </c>
       <c r="AN82" t="s" s="2">
-        <v>226</v>
+        <v>440</v>
       </c>
       <c r="AO82" t="s" s="2">
         <v>82</v>
@@ -12350,10 +12191,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>554</v>
+        <v>526</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12364,7 +12205,7 @@
         <v>80</v>
       </c>
       <c r="G83" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H83" t="s" s="2">
         <v>82</v>
@@ -12373,22 +12214,22 @@
         <v>82</v>
       </c>
       <c r="J83" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>379</v>
+        <v>191</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>380</v>
+        <v>527</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>381</v>
+        <v>528</v>
       </c>
       <c r="N83" t="s" s="2">
-        <v>382</v>
+        <v>529</v>
       </c>
       <c r="O83" t="s" s="2">
-        <v>383</v>
+        <v>530</v>
       </c>
       <c r="P83" t="s" s="2">
         <v>82</v>
@@ -12398,7 +12239,7 @@
         <v>82</v>
       </c>
       <c r="S83" t="s" s="2">
-        <v>555</v>
+        <v>82</v>
       </c>
       <c r="T83" t="s" s="2">
         <v>82</v>
@@ -12413,13 +12254,13 @@
         <v>82</v>
       </c>
       <c r="X83" t="s" s="2">
-        <v>82</v>
+        <v>212</v>
       </c>
       <c r="Y83" t="s" s="2">
-        <v>82</v>
+        <v>531</v>
       </c>
       <c r="Z83" t="s" s="2">
-        <v>82</v>
+        <v>532</v>
       </c>
       <c r="AA83" t="s" s="2">
         <v>82</v>
@@ -12437,13 +12278,13 @@
         <v>82</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>384</v>
+        <v>526</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH83" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI83" t="s" s="2">
         <v>82</v>
@@ -12455,13 +12296,13 @@
         <v>82</v>
       </c>
       <c r="AL83" t="s" s="2">
-        <v>82</v>
+        <v>524</v>
       </c>
       <c r="AM83" t="s" s="2">
-        <v>385</v>
+        <v>525</v>
       </c>
       <c r="AN83" t="s" s="2">
-        <v>386</v>
+        <v>440</v>
       </c>
       <c r="AO83" t="s" s="2">
         <v>82</v>
@@ -12472,10 +12313,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>556</v>
+        <v>553</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>557</v>
+        <v>533</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12486,36 +12327,34 @@
         <v>80</v>
       </c>
       <c r="G84" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="H84" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I84" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="J84" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>113</v>
+        <v>534</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>388</v>
+        <v>535</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>558</v>
+        <v>536</v>
       </c>
       <c r="N84" s="2"/>
       <c r="O84" t="s" s="2">
-        <v>390</v>
+        <v>537</v>
       </c>
       <c r="P84" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="Q84" t="s" s="2">
-        <v>391</v>
-      </c>
+      <c r="Q84" s="2"/>
       <c r="R84" t="s" s="2">
         <v>82</v>
       </c>
@@ -12535,13 +12374,13 @@
         <v>82</v>
       </c>
       <c r="X84" t="s" s="2">
-        <v>182</v>
+        <v>82</v>
       </c>
       <c r="Y84" t="s" s="2">
-        <v>392</v>
+        <v>82</v>
       </c>
       <c r="Z84" t="s" s="2">
-        <v>393</v>
+        <v>82</v>
       </c>
       <c r="AA84" t="s" s="2">
         <v>82</v>
@@ -12559,7 +12398,7 @@
         <v>82</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>394</v>
+        <v>533</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>80</v>
@@ -12580,10 +12419,10 @@
         <v>82</v>
       </c>
       <c r="AM84" t="s" s="2">
-        <v>395</v>
+        <v>82</v>
       </c>
       <c r="AN84" t="s" s="2">
-        <v>396</v>
+        <v>538</v>
       </c>
       <c r="AO84" t="s" s="2">
         <v>82</v>
@@ -12594,10 +12433,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>559</v>
+        <v>554</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>560</v>
+        <v>539</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12605,7 +12444,7 @@
       </c>
       <c r="E85" s="2"/>
       <c r="F85" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G85" t="s" s="2">
         <v>93</v>
@@ -12617,21 +12456,19 @@
         <v>82</v>
       </c>
       <c r="J85" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K85" t="s" s="2">
         <v>222</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>398</v>
+        <v>540</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>399</v>
+        <v>541</v>
       </c>
       <c r="N85" s="2"/>
-      <c r="O85" t="s" s="2">
-        <v>400</v>
-      </c>
+      <c r="O85" s="2"/>
       <c r="P85" t="s" s="2">
         <v>82</v>
       </c>
@@ -12640,7 +12477,7 @@
         <v>82</v>
       </c>
       <c r="S85" t="s" s="2">
-        <v>401</v>
+        <v>555</v>
       </c>
       <c r="T85" t="s" s="2">
         <v>82</v>
@@ -12679,7 +12516,7 @@
         <v>82</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>402</v>
+        <v>539</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>80</v>
@@ -12700,10 +12537,10 @@
         <v>82</v>
       </c>
       <c r="AM85" t="s" s="2">
-        <v>403</v>
+        <v>511</v>
       </c>
       <c r="AN85" t="s" s="2">
-        <v>404</v>
+        <v>542</v>
       </c>
       <c r="AO85" t="s" s="2">
         <v>82</v>
@@ -12714,12 +12551,14 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>561</v>
+        <v>556</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>562</v>
-      </c>
-      <c r="C86" s="2"/>
+        <v>487</v>
+      </c>
+      <c r="C86" t="s" s="2">
+        <v>557</v>
+      </c>
       <c r="D86" t="s" s="2">
         <v>82</v>
       </c>
@@ -12737,20 +12576,22 @@
         <v>82</v>
       </c>
       <c r="J86" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>107</v>
+        <v>488</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>406</v>
+        <v>489</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>407</v>
-      </c>
-      <c r="N86" s="2"/>
+        <v>490</v>
+      </c>
+      <c r="N86" t="s" s="2">
+        <v>491</v>
+      </c>
       <c r="O86" t="s" s="2">
-        <v>408</v>
+        <v>492</v>
       </c>
       <c r="P86" t="s" s="2">
         <v>82</v>
@@ -12760,7 +12601,7 @@
         <v>82</v>
       </c>
       <c r="S86" t="s" s="2">
-        <v>409</v>
+        <v>82</v>
       </c>
       <c r="T86" t="s" s="2">
         <v>82</v>
@@ -12799,19 +12640,19 @@
         <v>82</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>410</v>
+        <v>487</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH86" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI86" t="s" s="2">
-        <v>411</v>
+        <v>82</v>
       </c>
       <c r="AJ86" t="s" s="2">
-        <v>105</v>
+        <v>496</v>
       </c>
       <c r="AK86" t="s" s="2">
         <v>82</v>
@@ -12820,10 +12661,10 @@
         <v>82</v>
       </c>
       <c r="AM86" t="s" s="2">
-        <v>403</v>
+        <v>497</v>
       </c>
       <c r="AN86" t="s" s="2">
-        <v>412</v>
+        <v>498</v>
       </c>
       <c r="AO86" t="s" s="2">
         <v>82</v>
@@ -12834,10 +12675,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>563</v>
+        <v>558</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>564</v>
+        <v>499</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12857,23 +12698,19 @@
         <v>82</v>
       </c>
       <c r="J87" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>113</v>
+        <v>222</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>414</v>
+        <v>223</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>415</v>
-      </c>
-      <c r="N87" t="s" s="2">
-        <v>416</v>
-      </c>
-      <c r="O87" t="s" s="2">
-        <v>417</v>
-      </c>
+        <v>224</v>
+      </c>
+      <c r="N87" s="2"/>
+      <c r="O87" s="2"/>
       <c r="P87" t="s" s="2">
         <v>82</v>
       </c>
@@ -12882,7 +12719,7 @@
         <v>82</v>
       </c>
       <c r="S87" t="s" s="2">
-        <v>401</v>
+        <v>82</v>
       </c>
       <c r="T87" t="s" s="2">
         <v>82</v>
@@ -12921,7 +12758,7 @@
         <v>82</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>418</v>
+        <v>225</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>80</v>
@@ -12933,7 +12770,7 @@
         <v>82</v>
       </c>
       <c r="AJ87" t="s" s="2">
-        <v>105</v>
+        <v>82</v>
       </c>
       <c r="AK87" t="s" s="2">
         <v>82</v>
@@ -12942,10 +12779,10 @@
         <v>82</v>
       </c>
       <c r="AM87" t="s" s="2">
-        <v>403</v>
+        <v>82</v>
       </c>
       <c r="AN87" t="s" s="2">
-        <v>419</v>
+        <v>226</v>
       </c>
       <c r="AO87" t="s" s="2">
         <v>82</v>
@@ -12956,21 +12793,21 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>565</v>
+        <v>559</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>513</v>
+        <v>500</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
-        <v>82</v>
+        <v>138</v>
       </c>
       <c r="E88" s="2"/>
       <c r="F88" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G88" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H88" t="s" s="2">
         <v>82</v>
@@ -12982,15 +12819,17 @@
         <v>82</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>507</v>
+        <v>139</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>514</v>
+        <v>140</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>515</v>
-      </c>
-      <c r="N88" s="2"/>
+        <v>228</v>
+      </c>
+      <c r="N88" t="s" s="2">
+        <v>142</v>
+      </c>
       <c r="O88" s="2"/>
       <c r="P88" t="s" s="2">
         <v>82</v>
@@ -13039,19 +12878,19 @@
         <v>82</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>513</v>
+        <v>231</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH88" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI88" t="s" s="2">
-        <v>510</v>
+        <v>82</v>
       </c>
       <c r="AJ88" t="s" s="2">
-        <v>105</v>
+        <v>144</v>
       </c>
       <c r="AK88" t="s" s="2">
         <v>82</v>
@@ -13060,10 +12899,10 @@
         <v>82</v>
       </c>
       <c r="AM88" t="s" s="2">
-        <v>511</v>
+        <v>82</v>
       </c>
       <c r="AN88" t="s" s="2">
-        <v>516</v>
+        <v>226</v>
       </c>
       <c r="AO88" t="s" s="2">
         <v>82</v>
@@ -13074,45 +12913,45 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>566</v>
+        <v>560</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>517</v>
+        <v>501</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
-        <v>82</v>
+        <v>502</v>
       </c>
       <c r="E89" s="2"/>
       <c r="F89" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G89" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H89" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I89" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="J89" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>191</v>
+        <v>139</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>518</v>
+        <v>503</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>519</v>
+        <v>504</v>
       </c>
       <c r="N89" t="s" s="2">
-        <v>520</v>
+        <v>142</v>
       </c>
       <c r="O89" t="s" s="2">
-        <v>521</v>
+        <v>148</v>
       </c>
       <c r="P89" t="s" s="2">
         <v>82</v>
@@ -13137,13 +12976,13 @@
         <v>82</v>
       </c>
       <c r="X89" t="s" s="2">
-        <v>117</v>
+        <v>82</v>
       </c>
       <c r="Y89" t="s" s="2">
-        <v>522</v>
+        <v>82</v>
       </c>
       <c r="Z89" t="s" s="2">
-        <v>523</v>
+        <v>82</v>
       </c>
       <c r="AA89" t="s" s="2">
         <v>82</v>
@@ -13161,31 +13000,31 @@
         <v>82</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>517</v>
+        <v>505</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH89" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI89" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ89" t="s" s="2">
-        <v>105</v>
+        <v>144</v>
       </c>
       <c r="AK89" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL89" t="s" s="2">
-        <v>524</v>
+        <v>82</v>
       </c>
       <c r="AM89" t="s" s="2">
-        <v>525</v>
+        <v>82</v>
       </c>
       <c r="AN89" t="s" s="2">
-        <v>440</v>
+        <v>136</v>
       </c>
       <c r="AO89" t="s" s="2">
         <v>82</v>
@@ -13196,10 +13035,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>567</v>
+        <v>561</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>526</v>
+        <v>506</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -13210,7 +13049,7 @@
         <v>80</v>
       </c>
       <c r="G90" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H90" t="s" s="2">
         <v>82</v>
@@ -13222,20 +13061,16 @@
         <v>82</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>191</v>
+        <v>507</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>527</v>
+        <v>508</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>528</v>
-      </c>
-      <c r="N90" t="s" s="2">
-        <v>529</v>
-      </c>
-      <c r="O90" t="s" s="2">
-        <v>530</v>
-      </c>
+        <v>509</v>
+      </c>
+      <c r="N90" s="2"/>
+      <c r="O90" s="2"/>
       <c r="P90" t="s" s="2">
         <v>82</v>
       </c>
@@ -13259,13 +13094,13 @@
         <v>82</v>
       </c>
       <c r="X90" t="s" s="2">
-        <v>212</v>
+        <v>82</v>
       </c>
       <c r="Y90" t="s" s="2">
-        <v>531</v>
+        <v>82</v>
       </c>
       <c r="Z90" t="s" s="2">
-        <v>532</v>
+        <v>82</v>
       </c>
       <c r="AA90" t="s" s="2">
         <v>82</v>
@@ -13283,16 +13118,16 @@
         <v>82</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>526</v>
+        <v>506</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH90" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI90" t="s" s="2">
-        <v>82</v>
+        <v>510</v>
       </c>
       <c r="AJ90" t="s" s="2">
         <v>105</v>
@@ -13301,13 +13136,13 @@
         <v>82</v>
       </c>
       <c r="AL90" t="s" s="2">
-        <v>524</v>
+        <v>82</v>
       </c>
       <c r="AM90" t="s" s="2">
-        <v>525</v>
+        <v>511</v>
       </c>
       <c r="AN90" t="s" s="2">
-        <v>440</v>
+        <v>512</v>
       </c>
       <c r="AO90" t="s" s="2">
         <v>82</v>
@@ -13318,10 +13153,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>568</v>
+        <v>562</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>533</v>
+        <v>513</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -13344,18 +13179,16 @@
         <v>82</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>534</v>
+        <v>507</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>535</v>
+        <v>514</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>536</v>
+        <v>515</v>
       </c>
       <c r="N91" s="2"/>
-      <c r="O91" t="s" s="2">
-        <v>537</v>
-      </c>
+      <c r="O91" s="2"/>
       <c r="P91" t="s" s="2">
         <v>82</v>
       </c>
@@ -13364,7 +13197,7 @@
         <v>82</v>
       </c>
       <c r="S91" t="s" s="2">
-        <v>82</v>
+        <v>563</v>
       </c>
       <c r="T91" t="s" s="2">
         <v>82</v>
@@ -13403,7 +13236,7 @@
         <v>82</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>533</v>
+        <v>513</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>80</v>
@@ -13412,7 +13245,7 @@
         <v>93</v>
       </c>
       <c r="AI91" t="s" s="2">
-        <v>82</v>
+        <v>510</v>
       </c>
       <c r="AJ91" t="s" s="2">
         <v>105</v>
@@ -13424,10 +13257,10 @@
         <v>82</v>
       </c>
       <c r="AM91" t="s" s="2">
-        <v>82</v>
+        <v>511</v>
       </c>
       <c r="AN91" t="s" s="2">
-        <v>538</v>
+        <v>516</v>
       </c>
       <c r="AO91" t="s" s="2">
         <v>82</v>
@@ -13438,10 +13271,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>569</v>
+        <v>564</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>539</v>
+        <v>517</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -13449,7 +13282,7 @@
       </c>
       <c r="E92" s="2"/>
       <c r="F92" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G92" t="s" s="2">
         <v>93</v>
@@ -13464,16 +13297,20 @@
         <v>82</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>222</v>
+        <v>191</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>540</v>
+        <v>518</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>541</v>
-      </c>
-      <c r="N92" s="2"/>
-      <c r="O92" s="2"/>
+        <v>519</v>
+      </c>
+      <c r="N92" t="s" s="2">
+        <v>520</v>
+      </c>
+      <c r="O92" t="s" s="2">
+        <v>521</v>
+      </c>
       <c r="P92" t="s" s="2">
         <v>82</v>
       </c>
@@ -13482,7 +13319,7 @@
         <v>82</v>
       </c>
       <c r="S92" t="s" s="2">
-        <v>570</v>
+        <v>82</v>
       </c>
       <c r="T92" t="s" s="2">
         <v>82</v>
@@ -13497,13 +13334,13 @@
         <v>82</v>
       </c>
       <c r="X92" t="s" s="2">
-        <v>82</v>
+        <v>117</v>
       </c>
       <c r="Y92" t="s" s="2">
-        <v>82</v>
+        <v>522</v>
       </c>
       <c r="Z92" t="s" s="2">
-        <v>82</v>
+        <v>523</v>
       </c>
       <c r="AA92" t="s" s="2">
         <v>82</v>
@@ -13521,7 +13358,7 @@
         <v>82</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>539</v>
+        <v>517</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>80</v>
@@ -13539,13 +13376,13 @@
         <v>82</v>
       </c>
       <c r="AL92" t="s" s="2">
-        <v>82</v>
+        <v>524</v>
       </c>
       <c r="AM92" t="s" s="2">
-        <v>511</v>
+        <v>525</v>
       </c>
       <c r="AN92" t="s" s="2">
-        <v>542</v>
+        <v>440</v>
       </c>
       <c r="AO92" t="s" s="2">
         <v>82</v>
@@ -13556,14 +13393,12 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>571</v>
+        <v>565</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>487</v>
-      </c>
-      <c r="C93" t="s" s="2">
-        <v>572</v>
-      </c>
+        <v>526</v>
+      </c>
+      <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
         <v>82</v>
       </c>
@@ -13572,7 +13407,7 @@
         <v>80</v>
       </c>
       <c r="G93" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H93" t="s" s="2">
         <v>82</v>
@@ -13584,19 +13419,19 @@
         <v>82</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>488</v>
+        <v>191</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>489</v>
+        <v>527</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>490</v>
+        <v>528</v>
       </c>
       <c r="N93" t="s" s="2">
-        <v>491</v>
+        <v>529</v>
       </c>
       <c r="O93" t="s" s="2">
-        <v>492</v>
+        <v>530</v>
       </c>
       <c r="P93" t="s" s="2">
         <v>82</v>
@@ -13621,13 +13456,13 @@
         <v>82</v>
       </c>
       <c r="X93" t="s" s="2">
-        <v>82</v>
+        <v>212</v>
       </c>
       <c r="Y93" t="s" s="2">
-        <v>82</v>
+        <v>531</v>
       </c>
       <c r="Z93" t="s" s="2">
-        <v>82</v>
+        <v>532</v>
       </c>
       <c r="AA93" t="s" s="2">
         <v>82</v>
@@ -13645,7 +13480,7 @@
         <v>82</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>487</v>
+        <v>526</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>80</v>
@@ -13657,19 +13492,19 @@
         <v>82</v>
       </c>
       <c r="AJ93" t="s" s="2">
-        <v>496</v>
+        <v>105</v>
       </c>
       <c r="AK93" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL93" t="s" s="2">
-        <v>82</v>
+        <v>524</v>
       </c>
       <c r="AM93" t="s" s="2">
-        <v>497</v>
+        <v>525</v>
       </c>
       <c r="AN93" t="s" s="2">
-        <v>498</v>
+        <v>440</v>
       </c>
       <c r="AO93" t="s" s="2">
         <v>82</v>
@@ -13680,10 +13515,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>573</v>
+        <v>566</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>499</v>
+        <v>533</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13706,16 +13541,18 @@
         <v>82</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>222</v>
+        <v>534</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>223</v>
+        <v>535</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>224</v>
+        <v>536</v>
       </c>
       <c r="N94" s="2"/>
-      <c r="O94" s="2"/>
+      <c r="O94" t="s" s="2">
+        <v>537</v>
+      </c>
       <c r="P94" t="s" s="2">
         <v>82</v>
       </c>
@@ -13763,7 +13600,7 @@
         <v>82</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>225</v>
+        <v>533</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>80</v>
@@ -13775,7 +13612,7 @@
         <v>82</v>
       </c>
       <c r="AJ94" t="s" s="2">
-        <v>82</v>
+        <v>105</v>
       </c>
       <c r="AK94" t="s" s="2">
         <v>82</v>
@@ -13787,7 +13624,7 @@
         <v>82</v>
       </c>
       <c r="AN94" t="s" s="2">
-        <v>226</v>
+        <v>538</v>
       </c>
       <c r="AO94" t="s" s="2">
         <v>82</v>
@@ -13798,21 +13635,21 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>574</v>
+        <v>567</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>500</v>
+        <v>539</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
-        <v>138</v>
+        <v>82</v>
       </c>
       <c r="E95" s="2"/>
       <c r="F95" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G95" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H95" t="s" s="2">
         <v>82</v>
@@ -13824,17 +13661,15 @@
         <v>82</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>139</v>
+        <v>222</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>140</v>
+        <v>540</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>228</v>
-      </c>
-      <c r="N95" t="s" s="2">
-        <v>142</v>
-      </c>
+        <v>541</v>
+      </c>
+      <c r="N95" s="2"/>
       <c r="O95" s="2"/>
       <c r="P95" t="s" s="2">
         <v>82</v>
@@ -13844,7 +13679,7 @@
         <v>82</v>
       </c>
       <c r="S95" t="s" s="2">
-        <v>82</v>
+        <v>568</v>
       </c>
       <c r="T95" t="s" s="2">
         <v>82</v>
@@ -13883,19 +13718,19 @@
         <v>82</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>231</v>
+        <v>539</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH95" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI95" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ95" t="s" s="2">
-        <v>144</v>
+        <v>105</v>
       </c>
       <c r="AK95" t="s" s="2">
         <v>82</v>
@@ -13904,10 +13739,10 @@
         <v>82</v>
       </c>
       <c r="AM95" t="s" s="2">
-        <v>82</v>
+        <v>511</v>
       </c>
       <c r="AN95" t="s" s="2">
-        <v>226</v>
+        <v>542</v>
       </c>
       <c r="AO95" t="s" s="2">
         <v>82</v>
@@ -13918,14 +13753,14 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>575</v>
+        <v>569</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>501</v>
+        <v>569</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
-        <v>502</v>
+        <v>82</v>
       </c>
       <c r="E96" s="2"/>
       <c r="F96" t="s" s="2">
@@ -13938,26 +13773,24 @@
         <v>82</v>
       </c>
       <c r="I96" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="J96" t="s" s="2">
         <v>94</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>139</v>
+        <v>570</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>503</v>
+        <v>571</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>504</v>
+        <v>572</v>
       </c>
       <c r="N96" t="s" s="2">
-        <v>142</v>
-      </c>
-      <c r="O96" t="s" s="2">
-        <v>148</v>
-      </c>
+        <v>573</v>
+      </c>
+      <c r="O96" s="2"/>
       <c r="P96" t="s" s="2">
         <v>82</v>
       </c>
@@ -14005,7 +13838,7 @@
         <v>82</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>505</v>
+        <v>569</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>80</v>
@@ -14017,7 +13850,7 @@
         <v>82</v>
       </c>
       <c r="AJ96" t="s" s="2">
-        <v>144</v>
+        <v>105</v>
       </c>
       <c r="AK96" t="s" s="2">
         <v>82</v>
@@ -14026,10 +13859,10 @@
         <v>82</v>
       </c>
       <c r="AM96" t="s" s="2">
-        <v>82</v>
+        <v>574</v>
       </c>
       <c r="AN96" t="s" s="2">
-        <v>136</v>
+        <v>575</v>
       </c>
       <c r="AO96" t="s" s="2">
         <v>82</v>
@@ -14043,7 +13876,7 @@
         <v>576</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>506</v>
+        <v>576</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -14054,7 +13887,7 @@
         <v>80</v>
       </c>
       <c r="G97" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H97" t="s" s="2">
         <v>82</v>
@@ -14063,18 +13896,20 @@
         <v>82</v>
       </c>
       <c r="J97" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>507</v>
+        <v>577</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>508</v>
+        <v>578</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>509</v>
-      </c>
-      <c r="N97" s="2"/>
+        <v>579</v>
+      </c>
+      <c r="N97" t="s" s="2">
+        <v>580</v>
+      </c>
       <c r="O97" s="2"/>
       <c r="P97" t="s" s="2">
         <v>82</v>
@@ -14123,16 +13958,16 @@
         <v>82</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>506</v>
+        <v>576</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH97" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI97" t="s" s="2">
-        <v>510</v>
+        <v>82</v>
       </c>
       <c r="AJ97" t="s" s="2">
         <v>105</v>
@@ -14144,10 +13979,10 @@
         <v>82</v>
       </c>
       <c r="AM97" t="s" s="2">
-        <v>511</v>
+        <v>574</v>
       </c>
       <c r="AN97" t="s" s="2">
-        <v>512</v>
+        <v>581</v>
       </c>
       <c r="AO97" t="s" s="2">
         <v>82</v>
@@ -14158,10 +13993,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>577</v>
+        <v>582</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>550</v>
+        <v>582</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -14172,7 +14007,7 @@
         <v>80</v>
       </c>
       <c r="G98" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H98" t="s" s="2">
         <v>82</v>
@@ -14181,19 +14016,23 @@
         <v>82</v>
       </c>
       <c r="J98" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>222</v>
+        <v>488</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>223</v>
+        <v>583</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>224</v>
-      </c>
-      <c r="N98" s="2"/>
-      <c r="O98" s="2"/>
+        <v>584</v>
+      </c>
+      <c r="N98" t="s" s="2">
+        <v>585</v>
+      </c>
+      <c r="O98" t="s" s="2">
+        <v>586</v>
+      </c>
       <c r="P98" t="s" s="2">
         <v>82</v>
       </c>
@@ -14241,19 +14080,19 @@
         <v>82</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>225</v>
+        <v>582</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH98" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI98" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ98" t="s" s="2">
-        <v>82</v>
+        <v>105</v>
       </c>
       <c r="AK98" t="s" s="2">
         <v>82</v>
@@ -14262,10 +14101,10 @@
         <v>82</v>
       </c>
       <c r="AM98" t="s" s="2">
-        <v>82</v>
+        <v>587</v>
       </c>
       <c r="AN98" t="s" s="2">
-        <v>226</v>
+        <v>588</v>
       </c>
       <c r="AO98" t="s" s="2">
         <v>82</v>
@@ -14276,21 +14115,21 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>578</v>
+        <v>589</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>552</v>
+        <v>589</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
-        <v>138</v>
+        <v>82</v>
       </c>
       <c r="E99" s="2"/>
       <c r="F99" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G99" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H99" t="s" s="2">
         <v>82</v>
@@ -14302,17 +14141,15 @@
         <v>82</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>139</v>
+        <v>222</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>140</v>
+        <v>223</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>228</v>
-      </c>
-      <c r="N99" t="s" s="2">
-        <v>142</v>
-      </c>
+        <v>224</v>
+      </c>
+      <c r="N99" s="2"/>
       <c r="O99" s="2"/>
       <c r="P99" t="s" s="2">
         <v>82</v>
@@ -14349,31 +14186,31 @@
         <v>82</v>
       </c>
       <c r="AB99" t="s" s="2">
-        <v>229</v>
+        <v>82</v>
       </c>
       <c r="AC99" t="s" s="2">
-        <v>230</v>
+        <v>82</v>
       </c>
       <c r="AD99" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE99" t="s" s="2">
-        <v>199</v>
+        <v>82</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>231</v>
+        <v>225</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH99" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI99" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ99" t="s" s="2">
-        <v>144</v>
+        <v>82</v>
       </c>
       <c r="AK99" t="s" s="2">
         <v>82</v>
@@ -14396,21 +14233,21 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>579</v>
+        <v>590</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>554</v>
+        <v>590</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
-        <v>82</v>
+        <v>138</v>
       </c>
       <c r="E100" s="2"/>
       <c r="F100" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G100" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H100" t="s" s="2">
         <v>82</v>
@@ -14419,23 +14256,21 @@
         <v>82</v>
       </c>
       <c r="J100" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>379</v>
+        <v>139</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>380</v>
+        <v>140</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>381</v>
+        <v>228</v>
       </c>
       <c r="N100" t="s" s="2">
-        <v>382</v>
-      </c>
-      <c r="O100" t="s" s="2">
-        <v>383</v>
-      </c>
+        <v>142</v>
+      </c>
+      <c r="O100" s="2"/>
       <c r="P100" t="s" s="2">
         <v>82</v>
       </c>
@@ -14444,7 +14279,7 @@
         <v>82</v>
       </c>
       <c r="S100" t="s" s="2">
-        <v>580</v>
+        <v>82</v>
       </c>
       <c r="T100" t="s" s="2">
         <v>82</v>
@@ -14483,19 +14318,19 @@
         <v>82</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>384</v>
+        <v>231</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH100" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI100" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ100" t="s" s="2">
-        <v>105</v>
+        <v>144</v>
       </c>
       <c r="AK100" t="s" s="2">
         <v>82</v>
@@ -14504,10 +14339,10 @@
         <v>82</v>
       </c>
       <c r="AM100" t="s" s="2">
-        <v>385</v>
+        <v>82</v>
       </c>
       <c r="AN100" t="s" s="2">
-        <v>386</v>
+        <v>226</v>
       </c>
       <c r="AO100" t="s" s="2">
         <v>82</v>
@@ -14518,21 +14353,21 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>581</v>
+        <v>591</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>557</v>
+        <v>591</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
-        <v>82</v>
+        <v>502</v>
       </c>
       <c r="E101" s="2"/>
       <c r="F101" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G101" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H101" t="s" s="2">
         <v>82</v>
@@ -14544,24 +14379,24 @@
         <v>94</v>
       </c>
       <c r="K101" t="s" s="2">
-        <v>113</v>
+        <v>139</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>388</v>
+        <v>503</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>558</v>
-      </c>
-      <c r="N101" s="2"/>
+        <v>504</v>
+      </c>
+      <c r="N101" t="s" s="2">
+        <v>142</v>
+      </c>
       <c r="O101" t="s" s="2">
-        <v>390</v>
+        <v>148</v>
       </c>
       <c r="P101" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="Q101" t="s" s="2">
-        <v>391</v>
-      </c>
+      <c r="Q101" s="2"/>
       <c r="R101" t="s" s="2">
         <v>82</v>
       </c>
@@ -14581,13 +14416,13 @@
         <v>82</v>
       </c>
       <c r="X101" t="s" s="2">
-        <v>182</v>
+        <v>82</v>
       </c>
       <c r="Y101" t="s" s="2">
-        <v>392</v>
+        <v>82</v>
       </c>
       <c r="Z101" t="s" s="2">
-        <v>393</v>
+        <v>82</v>
       </c>
       <c r="AA101" t="s" s="2">
         <v>82</v>
@@ -14605,19 +14440,19 @@
         <v>82</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>394</v>
+        <v>505</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH101" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI101" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ101" t="s" s="2">
-        <v>105</v>
+        <v>144</v>
       </c>
       <c r="AK101" t="s" s="2">
         <v>82</v>
@@ -14626,10 +14461,10 @@
         <v>82</v>
       </c>
       <c r="AM101" t="s" s="2">
-        <v>395</v>
+        <v>82</v>
       </c>
       <c r="AN101" t="s" s="2">
-        <v>396</v>
+        <v>136</v>
       </c>
       <c r="AO101" t="s" s="2">
         <v>82</v>
@@ -14640,10 +14475,10 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>582</v>
+        <v>592</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>560</v>
+        <v>592</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -14651,7 +14486,7 @@
       </c>
       <c r="E102" s="2"/>
       <c r="F102" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G102" t="s" s="2">
         <v>93</v>
@@ -14666,17 +14501,19 @@
         <v>94</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>222</v>
+        <v>191</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>398</v>
+        <v>593</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>399</v>
-      </c>
-      <c r="N102" s="2"/>
+        <v>594</v>
+      </c>
+      <c r="N102" t="s" s="2">
+        <v>595</v>
+      </c>
       <c r="O102" t="s" s="2">
-        <v>400</v>
+        <v>211</v>
       </c>
       <c r="P102" t="s" s="2">
         <v>82</v>
@@ -14686,7 +14523,7 @@
         <v>82</v>
       </c>
       <c r="S102" t="s" s="2">
-        <v>401</v>
+        <v>82</v>
       </c>
       <c r="T102" t="s" s="2">
         <v>82</v>
@@ -14701,13 +14538,13 @@
         <v>82</v>
       </c>
       <c r="X102" t="s" s="2">
-        <v>82</v>
+        <v>212</v>
       </c>
       <c r="Y102" t="s" s="2">
-        <v>82</v>
+        <v>213</v>
       </c>
       <c r="Z102" t="s" s="2">
-        <v>82</v>
+        <v>214</v>
       </c>
       <c r="AA102" t="s" s="2">
         <v>82</v>
@@ -14725,10 +14562,10 @@
         <v>82</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>402</v>
+        <v>592</v>
       </c>
       <c r="AG102" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="AH102" t="s" s="2">
         <v>93</v>
@@ -14743,16 +14580,16 @@
         <v>82</v>
       </c>
       <c r="AL102" t="s" s="2">
-        <v>82</v>
+        <v>596</v>
       </c>
       <c r="AM102" t="s" s="2">
-        <v>403</v>
+        <v>217</v>
       </c>
       <c r="AN102" t="s" s="2">
-        <v>404</v>
+        <v>218</v>
       </c>
       <c r="AO102" t="s" s="2">
-        <v>82</v>
+        <v>219</v>
       </c>
       <c r="AP102" t="s" s="2">
         <v>82</v>
@@ -14760,10 +14597,10 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>583</v>
+        <v>597</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>562</v>
+        <v>597</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -14786,17 +14623,19 @@
         <v>94</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>107</v>
+        <v>598</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>406</v>
+        <v>599</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>407</v>
-      </c>
-      <c r="N103" s="2"/>
+        <v>368</v>
+      </c>
+      <c r="N103" t="s" s="2">
+        <v>600</v>
+      </c>
       <c r="O103" t="s" s="2">
-        <v>408</v>
+        <v>370</v>
       </c>
       <c r="P103" t="s" s="2">
         <v>82</v>
@@ -14806,7 +14645,7 @@
         <v>82</v>
       </c>
       <c r="S103" t="s" s="2">
-        <v>409</v>
+        <v>82</v>
       </c>
       <c r="T103" t="s" s="2">
         <v>82</v>
@@ -14845,7 +14684,7 @@
         <v>82</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>410</v>
+        <v>597</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>80</v>
@@ -14854,7 +14693,7 @@
         <v>93</v>
       </c>
       <c r="AI103" t="s" s="2">
-        <v>411</v>
+        <v>82</v>
       </c>
       <c r="AJ103" t="s" s="2">
         <v>105</v>
@@ -14863,27 +14702,27 @@
         <v>82</v>
       </c>
       <c r="AL103" t="s" s="2">
-        <v>82</v>
+        <v>601</v>
       </c>
       <c r="AM103" t="s" s="2">
-        <v>403</v>
+        <v>373</v>
       </c>
       <c r="AN103" t="s" s="2">
-        <v>412</v>
+        <v>374</v>
       </c>
       <c r="AO103" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP103" t="s" s="2">
-        <v>82</v>
+        <v>375</v>
       </c>
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>584</v>
+        <v>602</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>564</v>
+        <v>602</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -14903,22 +14742,22 @@
         <v>82</v>
       </c>
       <c r="J104" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>113</v>
+        <v>191</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>414</v>
+        <v>603</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>415</v>
+        <v>604</v>
       </c>
       <c r="N104" t="s" s="2">
-        <v>416</v>
+        <v>605</v>
       </c>
       <c r="O104" t="s" s="2">
-        <v>417</v>
+        <v>424</v>
       </c>
       <c r="P104" t="s" s="2">
         <v>82</v>
@@ -14928,7 +14767,7 @@
         <v>82</v>
       </c>
       <c r="S104" t="s" s="2">
-        <v>401</v>
+        <v>82</v>
       </c>
       <c r="T104" t="s" s="2">
         <v>82</v>
@@ -14943,13 +14782,13 @@
         <v>82</v>
       </c>
       <c r="X104" t="s" s="2">
-        <v>82</v>
+        <v>425</v>
       </c>
       <c r="Y104" t="s" s="2">
-        <v>82</v>
+        <v>426</v>
       </c>
       <c r="Z104" t="s" s="2">
-        <v>82</v>
+        <v>427</v>
       </c>
       <c r="AA104" t="s" s="2">
         <v>82</v>
@@ -14967,7 +14806,7 @@
         <v>82</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>418</v>
+        <v>602</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>80</v>
@@ -14976,7 +14815,7 @@
         <v>93</v>
       </c>
       <c r="AI104" t="s" s="2">
-        <v>82</v>
+        <v>428</v>
       </c>
       <c r="AJ104" t="s" s="2">
         <v>105</v>
@@ -14988,10 +14827,10 @@
         <v>82</v>
       </c>
       <c r="AM104" t="s" s="2">
-        <v>403</v>
+        <v>136</v>
       </c>
       <c r="AN104" t="s" s="2">
-        <v>419</v>
+        <v>429</v>
       </c>
       <c r="AO104" t="s" s="2">
         <v>82</v>
@@ -15002,21 +14841,21 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>585</v>
+        <v>606</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>513</v>
+        <v>606</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
-        <v>82</v>
+        <v>431</v>
       </c>
       <c r="E105" s="2"/>
       <c r="F105" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G105" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H105" t="s" s="2">
         <v>82</v>
@@ -15028,16 +14867,20 @@
         <v>82</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>507</v>
+        <v>191</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>514</v>
+        <v>432</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>515</v>
-      </c>
-      <c r="N105" s="2"/>
-      <c r="O105" s="2"/>
+        <v>433</v>
+      </c>
+      <c r="N105" t="s" s="2">
+        <v>434</v>
+      </c>
+      <c r="O105" t="s" s="2">
+        <v>435</v>
+      </c>
       <c r="P105" t="s" s="2">
         <v>82</v>
       </c>
@@ -15061,13 +14904,13 @@
         <v>82</v>
       </c>
       <c r="X105" t="s" s="2">
-        <v>82</v>
+        <v>425</v>
       </c>
       <c r="Y105" t="s" s="2">
-        <v>82</v>
+        <v>436</v>
       </c>
       <c r="Z105" t="s" s="2">
-        <v>82</v>
+        <v>437</v>
       </c>
       <c r="AA105" t="s" s="2">
         <v>82</v>
@@ -15085,16 +14928,16 @@
         <v>82</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>513</v>
+        <v>606</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH105" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI105" t="s" s="2">
-        <v>510</v>
+        <v>82</v>
       </c>
       <c r="AJ105" t="s" s="2">
         <v>105</v>
@@ -15103,27 +14946,27 @@
         <v>82</v>
       </c>
       <c r="AL105" t="s" s="2">
-        <v>82</v>
+        <v>438</v>
       </c>
       <c r="AM105" t="s" s="2">
-        <v>511</v>
+        <v>439</v>
       </c>
       <c r="AN105" t="s" s="2">
-        <v>516</v>
+        <v>440</v>
       </c>
       <c r="AO105" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP105" t="s" s="2">
-        <v>82</v>
+        <v>441</v>
       </c>
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>586</v>
+        <v>607</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>587</v>
+        <v>607</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -15134,7 +14977,7 @@
         <v>80</v>
       </c>
       <c r="G106" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H106" t="s" s="2">
         <v>82</v>
@@ -15146,16 +14989,20 @@
         <v>82</v>
       </c>
       <c r="K106" t="s" s="2">
-        <v>222</v>
+        <v>83</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>223</v>
+        <v>608</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>224</v>
-      </c>
-      <c r="N106" s="2"/>
-      <c r="O106" s="2"/>
+        <v>609</v>
+      </c>
+      <c r="N106" t="s" s="2">
+        <v>491</v>
+      </c>
+      <c r="O106" t="s" s="2">
+        <v>492</v>
+      </c>
       <c r="P106" t="s" s="2">
         <v>82</v>
       </c>
@@ -15203,19 +15050,19 @@
         <v>82</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>225</v>
+        <v>607</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH106" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI106" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ106" t="s" s="2">
-        <v>82</v>
+        <v>105</v>
       </c>
       <c r="AK106" t="s" s="2">
         <v>82</v>
@@ -15224,4606 +15071,20 @@
         <v>82</v>
       </c>
       <c r="AM106" t="s" s="2">
-        <v>82</v>
+        <v>497</v>
       </c>
       <c r="AN106" t="s" s="2">
-        <v>226</v>
+        <v>498</v>
       </c>
       <c r="AO106" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP106" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="107" hidden="true">
-      <c r="A107" t="s" s="2">
-        <v>588</v>
-      </c>
-      <c r="B107" t="s" s="2">
-        <v>589</v>
-      </c>
-      <c r="C107" s="2"/>
-      <c r="D107" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="E107" s="2"/>
-      <c r="F107" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G107" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H107" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I107" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J107" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="K107" t="s" s="2">
-        <v>139</v>
-      </c>
-      <c r="L107" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="M107" t="s" s="2">
-        <v>228</v>
-      </c>
-      <c r="N107" t="s" s="2">
-        <v>142</v>
-      </c>
-      <c r="O107" s="2"/>
-      <c r="P107" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q107" s="2"/>
-      <c r="R107" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S107" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T107" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U107" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V107" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W107" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X107" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y107" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z107" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA107" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB107" t="s" s="2">
-        <v>229</v>
-      </c>
-      <c r="AC107" t="s" s="2">
-        <v>230</v>
-      </c>
-      <c r="AD107" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE107" t="s" s="2">
-        <v>199</v>
-      </c>
-      <c r="AF107" t="s" s="2">
-        <v>231</v>
-      </c>
-      <c r="AG107" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH107" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI107" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ107" t="s" s="2">
-        <v>144</v>
-      </c>
-      <c r="AK107" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL107" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM107" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN107" t="s" s="2">
-        <v>226</v>
-      </c>
-      <c r="AO107" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP107" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="108" hidden="true">
-      <c r="A108" t="s" s="2">
-        <v>590</v>
-      </c>
-      <c r="B108" t="s" s="2">
-        <v>591</v>
-      </c>
-      <c r="C108" s="2"/>
-      <c r="D108" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="E108" s="2"/>
-      <c r="F108" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G108" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="H108" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I108" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J108" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="K108" t="s" s="2">
-        <v>379</v>
-      </c>
-      <c r="L108" t="s" s="2">
-        <v>380</v>
-      </c>
-      <c r="M108" t="s" s="2">
-        <v>381</v>
-      </c>
-      <c r="N108" t="s" s="2">
-        <v>382</v>
-      </c>
-      <c r="O108" t="s" s="2">
-        <v>383</v>
-      </c>
-      <c r="P108" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q108" s="2"/>
-      <c r="R108" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S108" t="s" s="2">
-        <v>592</v>
-      </c>
-      <c r="T108" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U108" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V108" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W108" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X108" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y108" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z108" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA108" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB108" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC108" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD108" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE108" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF108" t="s" s="2">
-        <v>384</v>
-      </c>
-      <c r="AG108" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH108" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AI108" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ108" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AK108" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL108" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM108" t="s" s="2">
-        <v>385</v>
-      </c>
-      <c r="AN108" t="s" s="2">
-        <v>386</v>
-      </c>
-      <c r="AO108" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP108" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="109" hidden="true">
-      <c r="A109" t="s" s="2">
-        <v>593</v>
-      </c>
-      <c r="B109" t="s" s="2">
-        <v>594</v>
-      </c>
-      <c r="C109" s="2"/>
-      <c r="D109" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="E109" s="2"/>
-      <c r="F109" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G109" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H109" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I109" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="J109" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="K109" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="L109" t="s" s="2">
-        <v>388</v>
-      </c>
-      <c r="M109" t="s" s="2">
-        <v>558</v>
-      </c>
-      <c r="N109" s="2"/>
-      <c r="O109" t="s" s="2">
-        <v>390</v>
-      </c>
-      <c r="P109" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q109" t="s" s="2">
-        <v>391</v>
-      </c>
-      <c r="R109" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S109" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T109" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U109" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V109" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W109" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X109" t="s" s="2">
-        <v>182</v>
-      </c>
-      <c r="Y109" t="s" s="2">
-        <v>392</v>
-      </c>
-      <c r="Z109" t="s" s="2">
-        <v>393</v>
-      </c>
-      <c r="AA109" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB109" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC109" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD109" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE109" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF109" t="s" s="2">
-        <v>394</v>
-      </c>
-      <c r="AG109" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH109" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AI109" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ109" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AK109" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL109" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM109" t="s" s="2">
-        <v>395</v>
-      </c>
-      <c r="AN109" t="s" s="2">
-        <v>396</v>
-      </c>
-      <c r="AO109" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP109" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="110" hidden="true">
-      <c r="A110" t="s" s="2">
-        <v>595</v>
-      </c>
-      <c r="B110" t="s" s="2">
-        <v>596</v>
-      </c>
-      <c r="C110" s="2"/>
-      <c r="D110" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="E110" s="2"/>
-      <c r="F110" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G110" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="H110" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I110" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J110" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="K110" t="s" s="2">
-        <v>222</v>
-      </c>
-      <c r="L110" t="s" s="2">
-        <v>398</v>
-      </c>
-      <c r="M110" t="s" s="2">
-        <v>399</v>
-      </c>
-      <c r="N110" s="2"/>
-      <c r="O110" t="s" s="2">
-        <v>400</v>
-      </c>
-      <c r="P110" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q110" s="2"/>
-      <c r="R110" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S110" t="s" s="2">
-        <v>401</v>
-      </c>
-      <c r="T110" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U110" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V110" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W110" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X110" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y110" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z110" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA110" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB110" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC110" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD110" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE110" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF110" t="s" s="2">
-        <v>402</v>
-      </c>
-      <c r="AG110" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH110" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AI110" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ110" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AK110" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL110" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM110" t="s" s="2">
-        <v>403</v>
-      </c>
-      <c r="AN110" t="s" s="2">
-        <v>404</v>
-      </c>
-      <c r="AO110" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP110" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="111" hidden="true">
-      <c r="A111" t="s" s="2">
-        <v>597</v>
-      </c>
-      <c r="B111" t="s" s="2">
-        <v>598</v>
-      </c>
-      <c r="C111" s="2"/>
-      <c r="D111" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="E111" s="2"/>
-      <c r="F111" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G111" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="H111" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I111" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J111" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="K111" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="L111" t="s" s="2">
-        <v>406</v>
-      </c>
-      <c r="M111" t="s" s="2">
-        <v>407</v>
-      </c>
-      <c r="N111" s="2"/>
-      <c r="O111" t="s" s="2">
-        <v>408</v>
-      </c>
-      <c r="P111" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q111" s="2"/>
-      <c r="R111" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S111" t="s" s="2">
-        <v>409</v>
-      </c>
-      <c r="T111" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U111" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V111" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W111" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X111" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y111" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z111" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA111" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB111" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC111" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD111" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE111" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF111" t="s" s="2">
-        <v>410</v>
-      </c>
-      <c r="AG111" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH111" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AI111" t="s" s="2">
-        <v>411</v>
-      </c>
-      <c r="AJ111" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AK111" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL111" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM111" t="s" s="2">
-        <v>403</v>
-      </c>
-      <c r="AN111" t="s" s="2">
-        <v>412</v>
-      </c>
-      <c r="AO111" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP111" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="112" hidden="true">
-      <c r="A112" t="s" s="2">
-        <v>599</v>
-      </c>
-      <c r="B112" t="s" s="2">
-        <v>600</v>
-      </c>
-      <c r="C112" s="2"/>
-      <c r="D112" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="E112" s="2"/>
-      <c r="F112" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G112" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="H112" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I112" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J112" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="K112" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="L112" t="s" s="2">
-        <v>414</v>
-      </c>
-      <c r="M112" t="s" s="2">
-        <v>415</v>
-      </c>
-      <c r="N112" t="s" s="2">
-        <v>416</v>
-      </c>
-      <c r="O112" t="s" s="2">
-        <v>417</v>
-      </c>
-      <c r="P112" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q112" s="2"/>
-      <c r="R112" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S112" t="s" s="2">
-        <v>401</v>
-      </c>
-      <c r="T112" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U112" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V112" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W112" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X112" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y112" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z112" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA112" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB112" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC112" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD112" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE112" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF112" t="s" s="2">
-        <v>418</v>
-      </c>
-      <c r="AG112" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH112" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AI112" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ112" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AK112" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL112" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM112" t="s" s="2">
-        <v>403</v>
-      </c>
-      <c r="AN112" t="s" s="2">
-        <v>419</v>
-      </c>
-      <c r="AO112" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP112" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="113" hidden="true">
-      <c r="A113" t="s" s="2">
-        <v>601</v>
-      </c>
-      <c r="B113" t="s" s="2">
-        <v>517</v>
-      </c>
-      <c r="C113" s="2"/>
-      <c r="D113" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="E113" s="2"/>
-      <c r="F113" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G113" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="H113" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I113" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J113" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="K113" t="s" s="2">
-        <v>191</v>
-      </c>
-      <c r="L113" t="s" s="2">
-        <v>518</v>
-      </c>
-      <c r="M113" t="s" s="2">
-        <v>519</v>
-      </c>
-      <c r="N113" t="s" s="2">
-        <v>520</v>
-      </c>
-      <c r="O113" t="s" s="2">
-        <v>521</v>
-      </c>
-      <c r="P113" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q113" s="2"/>
-      <c r="R113" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S113" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T113" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U113" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V113" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W113" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X113" t="s" s="2">
-        <v>117</v>
-      </c>
-      <c r="Y113" t="s" s="2">
-        <v>522</v>
-      </c>
-      <c r="Z113" t="s" s="2">
-        <v>523</v>
-      </c>
-      <c r="AA113" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB113" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC113" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD113" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE113" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF113" t="s" s="2">
-        <v>517</v>
-      </c>
-      <c r="AG113" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH113" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AI113" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ113" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AK113" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL113" t="s" s="2">
-        <v>524</v>
-      </c>
-      <c r="AM113" t="s" s="2">
-        <v>525</v>
-      </c>
-      <c r="AN113" t="s" s="2">
-        <v>440</v>
-      </c>
-      <c r="AO113" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP113" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="114" hidden="true">
-      <c r="A114" t="s" s="2">
-        <v>602</v>
-      </c>
-      <c r="B114" t="s" s="2">
-        <v>526</v>
-      </c>
-      <c r="C114" s="2"/>
-      <c r="D114" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="E114" s="2"/>
-      <c r="F114" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G114" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H114" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I114" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J114" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="K114" t="s" s="2">
-        <v>191</v>
-      </c>
-      <c r="L114" t="s" s="2">
-        <v>527</v>
-      </c>
-      <c r="M114" t="s" s="2">
-        <v>528</v>
-      </c>
-      <c r="N114" t="s" s="2">
-        <v>529</v>
-      </c>
-      <c r="O114" t="s" s="2">
-        <v>530</v>
-      </c>
-      <c r="P114" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q114" s="2"/>
-      <c r="R114" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S114" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T114" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U114" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V114" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W114" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X114" t="s" s="2">
-        <v>212</v>
-      </c>
-      <c r="Y114" t="s" s="2">
-        <v>531</v>
-      </c>
-      <c r="Z114" t="s" s="2">
-        <v>532</v>
-      </c>
-      <c r="AA114" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB114" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC114" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD114" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE114" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF114" t="s" s="2">
-        <v>526</v>
-      </c>
-      <c r="AG114" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH114" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI114" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ114" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AK114" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL114" t="s" s="2">
-        <v>524</v>
-      </c>
-      <c r="AM114" t="s" s="2">
-        <v>525</v>
-      </c>
-      <c r="AN114" t="s" s="2">
-        <v>440</v>
-      </c>
-      <c r="AO114" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP114" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="115" hidden="true">
-      <c r="A115" t="s" s="2">
-        <v>603</v>
-      </c>
-      <c r="B115" t="s" s="2">
-        <v>533</v>
-      </c>
-      <c r="C115" s="2"/>
-      <c r="D115" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="E115" s="2"/>
-      <c r="F115" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G115" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="H115" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I115" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J115" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="K115" t="s" s="2">
-        <v>534</v>
-      </c>
-      <c r="L115" t="s" s="2">
-        <v>535</v>
-      </c>
-      <c r="M115" t="s" s="2">
-        <v>536</v>
-      </c>
-      <c r="N115" s="2"/>
-      <c r="O115" t="s" s="2">
-        <v>537</v>
-      </c>
-      <c r="P115" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q115" s="2"/>
-      <c r="R115" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S115" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T115" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U115" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V115" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W115" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X115" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y115" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z115" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA115" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB115" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC115" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD115" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE115" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF115" t="s" s="2">
-        <v>533</v>
-      </c>
-      <c r="AG115" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH115" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AI115" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ115" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AK115" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL115" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM115" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN115" t="s" s="2">
-        <v>538</v>
-      </c>
-      <c r="AO115" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP115" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="116" hidden="true">
-      <c r="A116" t="s" s="2">
-        <v>604</v>
-      </c>
-      <c r="B116" t="s" s="2">
-        <v>539</v>
-      </c>
-      <c r="C116" s="2"/>
-      <c r="D116" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="E116" s="2"/>
-      <c r="F116" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="G116" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="H116" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I116" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J116" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="K116" t="s" s="2">
-        <v>222</v>
-      </c>
-      <c r="L116" t="s" s="2">
-        <v>540</v>
-      </c>
-      <c r="M116" t="s" s="2">
-        <v>541</v>
-      </c>
-      <c r="N116" s="2"/>
-      <c r="O116" s="2"/>
-      <c r="P116" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q116" s="2"/>
-      <c r="R116" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S116" t="s" s="2">
-        <v>605</v>
-      </c>
-      <c r="T116" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U116" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V116" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W116" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X116" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y116" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z116" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA116" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB116" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC116" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD116" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE116" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF116" t="s" s="2">
-        <v>539</v>
-      </c>
-      <c r="AG116" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH116" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AI116" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ116" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AK116" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL116" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM116" t="s" s="2">
-        <v>511</v>
-      </c>
-      <c r="AN116" t="s" s="2">
-        <v>542</v>
-      </c>
-      <c r="AO116" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP116" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="117" hidden="true">
-      <c r="A117" t="s" s="2">
-        <v>606</v>
-      </c>
-      <c r="B117" t="s" s="2">
-        <v>487</v>
-      </c>
-      <c r="C117" t="s" s="2">
-        <v>607</v>
-      </c>
-      <c r="D117" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="E117" s="2"/>
-      <c r="F117" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G117" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="H117" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I117" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J117" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="K117" t="s" s="2">
-        <v>488</v>
-      </c>
-      <c r="L117" t="s" s="2">
-        <v>489</v>
-      </c>
-      <c r="M117" t="s" s="2">
-        <v>490</v>
-      </c>
-      <c r="N117" t="s" s="2">
-        <v>491</v>
-      </c>
-      <c r="O117" t="s" s="2">
-        <v>492</v>
-      </c>
-      <c r="P117" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q117" s="2"/>
-      <c r="R117" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S117" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T117" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U117" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V117" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W117" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X117" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y117" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z117" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA117" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB117" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC117" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD117" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE117" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF117" t="s" s="2">
-        <v>487</v>
-      </c>
-      <c r="AG117" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH117" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI117" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ117" t="s" s="2">
-        <v>496</v>
-      </c>
-      <c r="AK117" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL117" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM117" t="s" s="2">
-        <v>497</v>
-      </c>
-      <c r="AN117" t="s" s="2">
-        <v>498</v>
-      </c>
-      <c r="AO117" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP117" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="118" hidden="true">
-      <c r="A118" t="s" s="2">
-        <v>608</v>
-      </c>
-      <c r="B118" t="s" s="2">
-        <v>499</v>
-      </c>
-      <c r="C118" s="2"/>
-      <c r="D118" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="E118" s="2"/>
-      <c r="F118" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G118" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="H118" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I118" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J118" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="K118" t="s" s="2">
-        <v>222</v>
-      </c>
-      <c r="L118" t="s" s="2">
-        <v>223</v>
-      </c>
-      <c r="M118" t="s" s="2">
-        <v>224</v>
-      </c>
-      <c r="N118" s="2"/>
-      <c r="O118" s="2"/>
-      <c r="P118" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q118" s="2"/>
-      <c r="R118" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S118" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T118" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U118" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V118" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W118" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X118" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y118" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z118" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA118" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB118" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC118" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD118" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE118" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF118" t="s" s="2">
-        <v>225</v>
-      </c>
-      <c r="AG118" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH118" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AI118" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ118" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AK118" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL118" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM118" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN118" t="s" s="2">
-        <v>226</v>
-      </c>
-      <c r="AO118" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP118" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="119" hidden="true">
-      <c r="A119" t="s" s="2">
-        <v>609</v>
-      </c>
-      <c r="B119" t="s" s="2">
-        <v>500</v>
-      </c>
-      <c r="C119" s="2"/>
-      <c r="D119" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="E119" s="2"/>
-      <c r="F119" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G119" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H119" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I119" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J119" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="K119" t="s" s="2">
-        <v>139</v>
-      </c>
-      <c r="L119" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="M119" t="s" s="2">
-        <v>228</v>
-      </c>
-      <c r="N119" t="s" s="2">
-        <v>142</v>
-      </c>
-      <c r="O119" s="2"/>
-      <c r="P119" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q119" s="2"/>
-      <c r="R119" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S119" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T119" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U119" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V119" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W119" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X119" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y119" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z119" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA119" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB119" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC119" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD119" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE119" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF119" t="s" s="2">
-        <v>231</v>
-      </c>
-      <c r="AG119" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH119" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI119" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ119" t="s" s="2">
-        <v>144</v>
-      </c>
-      <c r="AK119" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL119" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM119" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN119" t="s" s="2">
-        <v>226</v>
-      </c>
-      <c r="AO119" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP119" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="120" hidden="true">
-      <c r="A120" t="s" s="2">
-        <v>610</v>
-      </c>
-      <c r="B120" t="s" s="2">
-        <v>501</v>
-      </c>
-      <c r="C120" s="2"/>
-      <c r="D120" t="s" s="2">
-        <v>502</v>
-      </c>
-      <c r="E120" s="2"/>
-      <c r="F120" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G120" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H120" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I120" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="J120" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="K120" t="s" s="2">
-        <v>139</v>
-      </c>
-      <c r="L120" t="s" s="2">
-        <v>503</v>
-      </c>
-      <c r="M120" t="s" s="2">
-        <v>504</v>
-      </c>
-      <c r="N120" t="s" s="2">
-        <v>142</v>
-      </c>
-      <c r="O120" t="s" s="2">
-        <v>148</v>
-      </c>
-      <c r="P120" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q120" s="2"/>
-      <c r="R120" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S120" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T120" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U120" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V120" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W120" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X120" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y120" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z120" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA120" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB120" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC120" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD120" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE120" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF120" t="s" s="2">
-        <v>505</v>
-      </c>
-      <c r="AG120" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH120" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI120" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ120" t="s" s="2">
-        <v>144</v>
-      </c>
-      <c r="AK120" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL120" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM120" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN120" t="s" s="2">
-        <v>136</v>
-      </c>
-      <c r="AO120" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP120" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="121" hidden="true">
-      <c r="A121" t="s" s="2">
-        <v>611</v>
-      </c>
-      <c r="B121" t="s" s="2">
-        <v>506</v>
-      </c>
-      <c r="C121" s="2"/>
-      <c r="D121" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="E121" s="2"/>
-      <c r="F121" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G121" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="H121" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I121" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J121" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="K121" t="s" s="2">
-        <v>507</v>
-      </c>
-      <c r="L121" t="s" s="2">
-        <v>508</v>
-      </c>
-      <c r="M121" t="s" s="2">
-        <v>509</v>
-      </c>
-      <c r="N121" s="2"/>
-      <c r="O121" s="2"/>
-      <c r="P121" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q121" s="2"/>
-      <c r="R121" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S121" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T121" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U121" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V121" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W121" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X121" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y121" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z121" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA121" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB121" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC121" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD121" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE121" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF121" t="s" s="2">
-        <v>506</v>
-      </c>
-      <c r="AG121" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH121" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AI121" t="s" s="2">
-        <v>510</v>
-      </c>
-      <c r="AJ121" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AK121" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL121" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM121" t="s" s="2">
-        <v>511</v>
-      </c>
-      <c r="AN121" t="s" s="2">
-        <v>512</v>
-      </c>
-      <c r="AO121" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP121" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="122" hidden="true">
-      <c r="A122" t="s" s="2">
-        <v>612</v>
-      </c>
-      <c r="B122" t="s" s="2">
-        <v>513</v>
-      </c>
-      <c r="C122" s="2"/>
-      <c r="D122" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="E122" s="2"/>
-      <c r="F122" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G122" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="H122" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I122" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J122" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="K122" t="s" s="2">
-        <v>507</v>
-      </c>
-      <c r="L122" t="s" s="2">
-        <v>514</v>
-      </c>
-      <c r="M122" t="s" s="2">
-        <v>515</v>
-      </c>
-      <c r="N122" s="2"/>
-      <c r="O122" s="2"/>
-      <c r="P122" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q122" s="2"/>
-      <c r="R122" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S122" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T122" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U122" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V122" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W122" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X122" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y122" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z122" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA122" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB122" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC122" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD122" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE122" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF122" t="s" s="2">
-        <v>513</v>
-      </c>
-      <c r="AG122" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH122" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AI122" t="s" s="2">
-        <v>510</v>
-      </c>
-      <c r="AJ122" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AK122" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL122" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM122" t="s" s="2">
-        <v>511</v>
-      </c>
-      <c r="AN122" t="s" s="2">
-        <v>516</v>
-      </c>
-      <c r="AO122" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP122" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="123" hidden="true">
-      <c r="A123" t="s" s="2">
-        <v>613</v>
-      </c>
-      <c r="B123" t="s" s="2">
-        <v>587</v>
-      </c>
-      <c r="C123" s="2"/>
-      <c r="D123" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="E123" s="2"/>
-      <c r="F123" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G123" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="H123" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I123" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J123" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="K123" t="s" s="2">
-        <v>222</v>
-      </c>
-      <c r="L123" t="s" s="2">
-        <v>223</v>
-      </c>
-      <c r="M123" t="s" s="2">
-        <v>224</v>
-      </c>
-      <c r="N123" s="2"/>
-      <c r="O123" s="2"/>
-      <c r="P123" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q123" s="2"/>
-      <c r="R123" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S123" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T123" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U123" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V123" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W123" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X123" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y123" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z123" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA123" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB123" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC123" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD123" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE123" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF123" t="s" s="2">
-        <v>225</v>
-      </c>
-      <c r="AG123" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH123" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AI123" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ123" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AK123" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL123" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM123" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN123" t="s" s="2">
-        <v>226</v>
-      </c>
-      <c r="AO123" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP123" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="124" hidden="true">
-      <c r="A124" t="s" s="2">
-        <v>614</v>
-      </c>
-      <c r="B124" t="s" s="2">
-        <v>589</v>
-      </c>
-      <c r="C124" s="2"/>
-      <c r="D124" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="E124" s="2"/>
-      <c r="F124" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G124" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H124" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I124" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J124" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="K124" t="s" s="2">
-        <v>139</v>
-      </c>
-      <c r="L124" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="M124" t="s" s="2">
-        <v>228</v>
-      </c>
-      <c r="N124" t="s" s="2">
-        <v>142</v>
-      </c>
-      <c r="O124" s="2"/>
-      <c r="P124" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q124" s="2"/>
-      <c r="R124" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S124" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T124" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U124" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V124" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W124" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X124" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y124" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z124" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA124" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB124" t="s" s="2">
-        <v>229</v>
-      </c>
-      <c r="AC124" t="s" s="2">
-        <v>230</v>
-      </c>
-      <c r="AD124" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE124" t="s" s="2">
-        <v>199</v>
-      </c>
-      <c r="AF124" t="s" s="2">
-        <v>231</v>
-      </c>
-      <c r="AG124" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH124" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI124" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ124" t="s" s="2">
-        <v>144</v>
-      </c>
-      <c r="AK124" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL124" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM124" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN124" t="s" s="2">
-        <v>226</v>
-      </c>
-      <c r="AO124" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP124" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="125" hidden="true">
-      <c r="A125" t="s" s="2">
-        <v>615</v>
-      </c>
-      <c r="B125" t="s" s="2">
-        <v>591</v>
-      </c>
-      <c r="C125" s="2"/>
-      <c r="D125" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="E125" s="2"/>
-      <c r="F125" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G125" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="H125" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I125" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J125" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="K125" t="s" s="2">
-        <v>379</v>
-      </c>
-      <c r="L125" t="s" s="2">
-        <v>380</v>
-      </c>
-      <c r="M125" t="s" s="2">
-        <v>381</v>
-      </c>
-      <c r="N125" t="s" s="2">
-        <v>382</v>
-      </c>
-      <c r="O125" t="s" s="2">
-        <v>383</v>
-      </c>
-      <c r="P125" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q125" s="2"/>
-      <c r="R125" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S125" t="s" s="2">
-        <v>616</v>
-      </c>
-      <c r="T125" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U125" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V125" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W125" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X125" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y125" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z125" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA125" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB125" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC125" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD125" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE125" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF125" t="s" s="2">
-        <v>384</v>
-      </c>
-      <c r="AG125" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH125" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AI125" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ125" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AK125" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL125" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM125" t="s" s="2">
-        <v>385</v>
-      </c>
-      <c r="AN125" t="s" s="2">
-        <v>386</v>
-      </c>
-      <c r="AO125" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP125" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="126" hidden="true">
-      <c r="A126" t="s" s="2">
-        <v>617</v>
-      </c>
-      <c r="B126" t="s" s="2">
-        <v>594</v>
-      </c>
-      <c r="C126" s="2"/>
-      <c r="D126" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="E126" s="2"/>
-      <c r="F126" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G126" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H126" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I126" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="J126" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="K126" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="L126" t="s" s="2">
-        <v>388</v>
-      </c>
-      <c r="M126" t="s" s="2">
-        <v>558</v>
-      </c>
-      <c r="N126" s="2"/>
-      <c r="O126" t="s" s="2">
-        <v>390</v>
-      </c>
-      <c r="P126" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q126" t="s" s="2">
-        <v>391</v>
-      </c>
-      <c r="R126" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S126" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T126" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U126" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V126" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W126" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X126" t="s" s="2">
-        <v>182</v>
-      </c>
-      <c r="Y126" t="s" s="2">
-        <v>392</v>
-      </c>
-      <c r="Z126" t="s" s="2">
-        <v>393</v>
-      </c>
-      <c r="AA126" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB126" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC126" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD126" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE126" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF126" t="s" s="2">
-        <v>394</v>
-      </c>
-      <c r="AG126" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH126" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AI126" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ126" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AK126" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL126" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM126" t="s" s="2">
-        <v>395</v>
-      </c>
-      <c r="AN126" t="s" s="2">
-        <v>396</v>
-      </c>
-      <c r="AO126" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP126" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="127" hidden="true">
-      <c r="A127" t="s" s="2">
-        <v>618</v>
-      </c>
-      <c r="B127" t="s" s="2">
-        <v>596</v>
-      </c>
-      <c r="C127" s="2"/>
-      <c r="D127" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="E127" s="2"/>
-      <c r="F127" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G127" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="H127" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I127" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J127" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="K127" t="s" s="2">
-        <v>222</v>
-      </c>
-      <c r="L127" t="s" s="2">
-        <v>398</v>
-      </c>
-      <c r="M127" t="s" s="2">
-        <v>399</v>
-      </c>
-      <c r="N127" s="2"/>
-      <c r="O127" t="s" s="2">
-        <v>400</v>
-      </c>
-      <c r="P127" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q127" s="2"/>
-      <c r="R127" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S127" t="s" s="2">
-        <v>401</v>
-      </c>
-      <c r="T127" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U127" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V127" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W127" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X127" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y127" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z127" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA127" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB127" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC127" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD127" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE127" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF127" t="s" s="2">
-        <v>402</v>
-      </c>
-      <c r="AG127" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH127" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AI127" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ127" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AK127" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL127" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM127" t="s" s="2">
-        <v>403</v>
-      </c>
-      <c r="AN127" t="s" s="2">
-        <v>404</v>
-      </c>
-      <c r="AO127" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP127" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="128" hidden="true">
-      <c r="A128" t="s" s="2">
-        <v>619</v>
-      </c>
-      <c r="B128" t="s" s="2">
-        <v>598</v>
-      </c>
-      <c r="C128" s="2"/>
-      <c r="D128" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="E128" s="2"/>
-      <c r="F128" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G128" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="H128" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I128" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J128" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="K128" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="L128" t="s" s="2">
-        <v>406</v>
-      </c>
-      <c r="M128" t="s" s="2">
-        <v>407</v>
-      </c>
-      <c r="N128" s="2"/>
-      <c r="O128" t="s" s="2">
-        <v>408</v>
-      </c>
-      <c r="P128" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q128" s="2"/>
-      <c r="R128" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S128" t="s" s="2">
-        <v>409</v>
-      </c>
-      <c r="T128" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U128" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V128" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W128" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X128" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y128" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z128" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA128" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB128" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC128" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD128" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE128" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF128" t="s" s="2">
-        <v>410</v>
-      </c>
-      <c r="AG128" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH128" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AI128" t="s" s="2">
-        <v>411</v>
-      </c>
-      <c r="AJ128" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AK128" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL128" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM128" t="s" s="2">
-        <v>403</v>
-      </c>
-      <c r="AN128" t="s" s="2">
-        <v>412</v>
-      </c>
-      <c r="AO128" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP128" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="129" hidden="true">
-      <c r="A129" t="s" s="2">
-        <v>620</v>
-      </c>
-      <c r="B129" t="s" s="2">
-        <v>600</v>
-      </c>
-      <c r="C129" s="2"/>
-      <c r="D129" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="E129" s="2"/>
-      <c r="F129" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G129" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="H129" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I129" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J129" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="K129" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="L129" t="s" s="2">
-        <v>414</v>
-      </c>
-      <c r="M129" t="s" s="2">
-        <v>415</v>
-      </c>
-      <c r="N129" t="s" s="2">
-        <v>416</v>
-      </c>
-      <c r="O129" t="s" s="2">
-        <v>417</v>
-      </c>
-      <c r="P129" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q129" s="2"/>
-      <c r="R129" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S129" t="s" s="2">
-        <v>401</v>
-      </c>
-      <c r="T129" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U129" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V129" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W129" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X129" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y129" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z129" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA129" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB129" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC129" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD129" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE129" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF129" t="s" s="2">
-        <v>418</v>
-      </c>
-      <c r="AG129" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH129" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AI129" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ129" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AK129" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL129" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM129" t="s" s="2">
-        <v>403</v>
-      </c>
-      <c r="AN129" t="s" s="2">
-        <v>419</v>
-      </c>
-      <c r="AO129" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP129" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="130" hidden="true">
-      <c r="A130" t="s" s="2">
-        <v>621</v>
-      </c>
-      <c r="B130" t="s" s="2">
-        <v>517</v>
-      </c>
-      <c r="C130" s="2"/>
-      <c r="D130" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="E130" s="2"/>
-      <c r="F130" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G130" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="H130" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I130" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J130" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="K130" t="s" s="2">
-        <v>191</v>
-      </c>
-      <c r="L130" t="s" s="2">
-        <v>518</v>
-      </c>
-      <c r="M130" t="s" s="2">
-        <v>519</v>
-      </c>
-      <c r="N130" t="s" s="2">
-        <v>520</v>
-      </c>
-      <c r="O130" t="s" s="2">
-        <v>521</v>
-      </c>
-      <c r="P130" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q130" s="2"/>
-      <c r="R130" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S130" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T130" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U130" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V130" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W130" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X130" t="s" s="2">
-        <v>117</v>
-      </c>
-      <c r="Y130" t="s" s="2">
-        <v>522</v>
-      </c>
-      <c r="Z130" t="s" s="2">
-        <v>523</v>
-      </c>
-      <c r="AA130" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB130" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC130" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD130" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE130" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF130" t="s" s="2">
-        <v>517</v>
-      </c>
-      <c r="AG130" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH130" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AI130" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ130" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AK130" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL130" t="s" s="2">
-        <v>524</v>
-      </c>
-      <c r="AM130" t="s" s="2">
-        <v>525</v>
-      </c>
-      <c r="AN130" t="s" s="2">
-        <v>440</v>
-      </c>
-      <c r="AO130" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP130" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="131" hidden="true">
-      <c r="A131" t="s" s="2">
-        <v>622</v>
-      </c>
-      <c r="B131" t="s" s="2">
-        <v>526</v>
-      </c>
-      <c r="C131" s="2"/>
-      <c r="D131" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="E131" s="2"/>
-      <c r="F131" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G131" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H131" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I131" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J131" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="K131" t="s" s="2">
-        <v>191</v>
-      </c>
-      <c r="L131" t="s" s="2">
-        <v>527</v>
-      </c>
-      <c r="M131" t="s" s="2">
-        <v>528</v>
-      </c>
-      <c r="N131" t="s" s="2">
-        <v>529</v>
-      </c>
-      <c r="O131" t="s" s="2">
-        <v>530</v>
-      </c>
-      <c r="P131" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q131" s="2"/>
-      <c r="R131" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S131" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T131" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U131" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V131" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W131" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X131" t="s" s="2">
-        <v>212</v>
-      </c>
-      <c r="Y131" t="s" s="2">
-        <v>531</v>
-      </c>
-      <c r="Z131" t="s" s="2">
-        <v>532</v>
-      </c>
-      <c r="AA131" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB131" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC131" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD131" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE131" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF131" t="s" s="2">
-        <v>526</v>
-      </c>
-      <c r="AG131" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH131" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI131" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ131" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AK131" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL131" t="s" s="2">
-        <v>524</v>
-      </c>
-      <c r="AM131" t="s" s="2">
-        <v>525</v>
-      </c>
-      <c r="AN131" t="s" s="2">
-        <v>440</v>
-      </c>
-      <c r="AO131" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP131" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="132" hidden="true">
-      <c r="A132" t="s" s="2">
-        <v>623</v>
-      </c>
-      <c r="B132" t="s" s="2">
-        <v>533</v>
-      </c>
-      <c r="C132" s="2"/>
-      <c r="D132" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="E132" s="2"/>
-      <c r="F132" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G132" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="H132" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I132" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J132" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="K132" t="s" s="2">
-        <v>534</v>
-      </c>
-      <c r="L132" t="s" s="2">
-        <v>535</v>
-      </c>
-      <c r="M132" t="s" s="2">
-        <v>536</v>
-      </c>
-      <c r="N132" s="2"/>
-      <c r="O132" t="s" s="2">
-        <v>537</v>
-      </c>
-      <c r="P132" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q132" s="2"/>
-      <c r="R132" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S132" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T132" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U132" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V132" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W132" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X132" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y132" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z132" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA132" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB132" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC132" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD132" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE132" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF132" t="s" s="2">
-        <v>533</v>
-      </c>
-      <c r="AG132" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH132" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AI132" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ132" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AK132" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL132" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM132" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN132" t="s" s="2">
-        <v>538</v>
-      </c>
-      <c r="AO132" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP132" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="133" hidden="true">
-      <c r="A133" t="s" s="2">
-        <v>624</v>
-      </c>
-      <c r="B133" t="s" s="2">
-        <v>539</v>
-      </c>
-      <c r="C133" s="2"/>
-      <c r="D133" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="E133" s="2"/>
-      <c r="F133" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="G133" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="H133" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I133" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J133" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="K133" t="s" s="2">
-        <v>222</v>
-      </c>
-      <c r="L133" t="s" s="2">
-        <v>540</v>
-      </c>
-      <c r="M133" t="s" s="2">
-        <v>541</v>
-      </c>
-      <c r="N133" s="2"/>
-      <c r="O133" s="2"/>
-      <c r="P133" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q133" s="2"/>
-      <c r="R133" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S133" t="s" s="2">
-        <v>625</v>
-      </c>
-      <c r="T133" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U133" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V133" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W133" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X133" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y133" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z133" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA133" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB133" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC133" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD133" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE133" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF133" t="s" s="2">
-        <v>539</v>
-      </c>
-      <c r="AG133" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH133" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AI133" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ133" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AK133" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL133" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM133" t="s" s="2">
-        <v>511</v>
-      </c>
-      <c r="AN133" t="s" s="2">
-        <v>542</v>
-      </c>
-      <c r="AO133" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP133" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="134" hidden="true">
-      <c r="A134" t="s" s="2">
-        <v>626</v>
-      </c>
-      <c r="B134" t="s" s="2">
-        <v>626</v>
-      </c>
-      <c r="C134" s="2"/>
-      <c r="D134" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="E134" s="2"/>
-      <c r="F134" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G134" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H134" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I134" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J134" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="K134" t="s" s="2">
-        <v>627</v>
-      </c>
-      <c r="L134" t="s" s="2">
-        <v>628</v>
-      </c>
-      <c r="M134" t="s" s="2">
-        <v>629</v>
-      </c>
-      <c r="N134" t="s" s="2">
-        <v>630</v>
-      </c>
-      <c r="O134" s="2"/>
-      <c r="P134" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q134" s="2"/>
-      <c r="R134" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S134" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T134" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U134" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V134" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W134" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X134" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y134" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z134" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA134" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB134" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC134" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD134" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE134" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF134" t="s" s="2">
-        <v>626</v>
-      </c>
-      <c r="AG134" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH134" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI134" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ134" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AK134" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL134" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM134" t="s" s="2">
-        <v>631</v>
-      </c>
-      <c r="AN134" t="s" s="2">
-        <v>632</v>
-      </c>
-      <c r="AO134" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP134" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="135" hidden="true">
-      <c r="A135" t="s" s="2">
-        <v>633</v>
-      </c>
-      <c r="B135" t="s" s="2">
-        <v>633</v>
-      </c>
-      <c r="C135" s="2"/>
-      <c r="D135" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="E135" s="2"/>
-      <c r="F135" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G135" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H135" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I135" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J135" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="K135" t="s" s="2">
-        <v>634</v>
-      </c>
-      <c r="L135" t="s" s="2">
-        <v>635</v>
-      </c>
-      <c r="M135" t="s" s="2">
-        <v>636</v>
-      </c>
-      <c r="N135" t="s" s="2">
-        <v>637</v>
-      </c>
-      <c r="O135" s="2"/>
-      <c r="P135" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q135" s="2"/>
-      <c r="R135" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S135" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T135" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U135" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V135" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W135" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X135" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y135" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z135" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA135" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB135" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC135" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD135" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE135" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF135" t="s" s="2">
-        <v>633</v>
-      </c>
-      <c r="AG135" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH135" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI135" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ135" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AK135" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL135" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM135" t="s" s="2">
-        <v>631</v>
-      </c>
-      <c r="AN135" t="s" s="2">
-        <v>638</v>
-      </c>
-      <c r="AO135" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP135" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="136" hidden="true">
-      <c r="A136" t="s" s="2">
-        <v>639</v>
-      </c>
-      <c r="B136" t="s" s="2">
-        <v>639</v>
-      </c>
-      <c r="C136" s="2"/>
-      <c r="D136" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="E136" s="2"/>
-      <c r="F136" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G136" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H136" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I136" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J136" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="K136" t="s" s="2">
-        <v>488</v>
-      </c>
-      <c r="L136" t="s" s="2">
-        <v>640</v>
-      </c>
-      <c r="M136" t="s" s="2">
-        <v>641</v>
-      </c>
-      <c r="N136" t="s" s="2">
-        <v>642</v>
-      </c>
-      <c r="O136" t="s" s="2">
-        <v>643</v>
-      </c>
-      <c r="P136" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q136" s="2"/>
-      <c r="R136" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S136" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T136" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U136" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V136" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W136" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X136" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y136" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z136" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA136" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB136" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC136" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD136" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE136" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF136" t="s" s="2">
-        <v>639</v>
-      </c>
-      <c r="AG136" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH136" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI136" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ136" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AK136" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL136" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM136" t="s" s="2">
-        <v>644</v>
-      </c>
-      <c r="AN136" t="s" s="2">
-        <v>645</v>
-      </c>
-      <c r="AO136" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP136" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="137" hidden="true">
-      <c r="A137" t="s" s="2">
-        <v>646</v>
-      </c>
-      <c r="B137" t="s" s="2">
-        <v>646</v>
-      </c>
-      <c r="C137" s="2"/>
-      <c r="D137" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="E137" s="2"/>
-      <c r="F137" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G137" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="H137" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I137" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J137" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="K137" t="s" s="2">
-        <v>222</v>
-      </c>
-      <c r="L137" t="s" s="2">
-        <v>223</v>
-      </c>
-      <c r="M137" t="s" s="2">
-        <v>224</v>
-      </c>
-      <c r="N137" s="2"/>
-      <c r="O137" s="2"/>
-      <c r="P137" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q137" s="2"/>
-      <c r="R137" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S137" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T137" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U137" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V137" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W137" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X137" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y137" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z137" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA137" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB137" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC137" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD137" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE137" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF137" t="s" s="2">
-        <v>225</v>
-      </c>
-      <c r="AG137" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH137" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AI137" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ137" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AK137" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL137" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM137" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN137" t="s" s="2">
-        <v>226</v>
-      </c>
-      <c r="AO137" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP137" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="138" hidden="true">
-      <c r="A138" t="s" s="2">
-        <v>647</v>
-      </c>
-      <c r="B138" t="s" s="2">
-        <v>647</v>
-      </c>
-      <c r="C138" s="2"/>
-      <c r="D138" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="E138" s="2"/>
-      <c r="F138" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G138" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H138" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I138" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J138" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="K138" t="s" s="2">
-        <v>139</v>
-      </c>
-      <c r="L138" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="M138" t="s" s="2">
-        <v>228</v>
-      </c>
-      <c r="N138" t="s" s="2">
-        <v>142</v>
-      </c>
-      <c r="O138" s="2"/>
-      <c r="P138" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q138" s="2"/>
-      <c r="R138" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S138" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T138" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U138" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V138" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W138" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X138" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y138" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z138" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA138" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB138" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC138" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD138" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE138" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF138" t="s" s="2">
-        <v>231</v>
-      </c>
-      <c r="AG138" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH138" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI138" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ138" t="s" s="2">
-        <v>144</v>
-      </c>
-      <c r="AK138" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL138" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM138" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN138" t="s" s="2">
-        <v>226</v>
-      </c>
-      <c r="AO138" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP138" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="139" hidden="true">
-      <c r="A139" t="s" s="2">
-        <v>648</v>
-      </c>
-      <c r="B139" t="s" s="2">
-        <v>648</v>
-      </c>
-      <c r="C139" s="2"/>
-      <c r="D139" t="s" s="2">
-        <v>502</v>
-      </c>
-      <c r="E139" s="2"/>
-      <c r="F139" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G139" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H139" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I139" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="J139" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="K139" t="s" s="2">
-        <v>139</v>
-      </c>
-      <c r="L139" t="s" s="2">
-        <v>503</v>
-      </c>
-      <c r="M139" t="s" s="2">
-        <v>504</v>
-      </c>
-      <c r="N139" t="s" s="2">
-        <v>142</v>
-      </c>
-      <c r="O139" t="s" s="2">
-        <v>148</v>
-      </c>
-      <c r="P139" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q139" s="2"/>
-      <c r="R139" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S139" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T139" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U139" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V139" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W139" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X139" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y139" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z139" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA139" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB139" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC139" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD139" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE139" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF139" t="s" s="2">
-        <v>505</v>
-      </c>
-      <c r="AG139" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH139" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI139" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ139" t="s" s="2">
-        <v>144</v>
-      </c>
-      <c r="AK139" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL139" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM139" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN139" t="s" s="2">
-        <v>136</v>
-      </c>
-      <c r="AO139" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP139" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="140" hidden="true">
-      <c r="A140" t="s" s="2">
-        <v>649</v>
-      </c>
-      <c r="B140" t="s" s="2">
-        <v>649</v>
-      </c>
-      <c r="C140" s="2"/>
-      <c r="D140" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="E140" s="2"/>
-      <c r="F140" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="G140" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="H140" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I140" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J140" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="K140" t="s" s="2">
-        <v>191</v>
-      </c>
-      <c r="L140" t="s" s="2">
-        <v>650</v>
-      </c>
-      <c r="M140" t="s" s="2">
-        <v>651</v>
-      </c>
-      <c r="N140" t="s" s="2">
-        <v>652</v>
-      </c>
-      <c r="O140" t="s" s="2">
-        <v>211</v>
-      </c>
-      <c r="P140" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q140" s="2"/>
-      <c r="R140" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S140" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T140" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U140" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V140" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W140" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X140" t="s" s="2">
-        <v>212</v>
-      </c>
-      <c r="Y140" t="s" s="2">
-        <v>213</v>
-      </c>
-      <c r="Z140" t="s" s="2">
-        <v>214</v>
-      </c>
-      <c r="AA140" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB140" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC140" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD140" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE140" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF140" t="s" s="2">
-        <v>649</v>
-      </c>
-      <c r="AG140" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AH140" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AI140" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ140" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AK140" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL140" t="s" s="2">
-        <v>653</v>
-      </c>
-      <c r="AM140" t="s" s="2">
-        <v>217</v>
-      </c>
-      <c r="AN140" t="s" s="2">
-        <v>218</v>
-      </c>
-      <c r="AO140" t="s" s="2">
-        <v>219</v>
-      </c>
-      <c r="AP140" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="141" hidden="true">
-      <c r="A141" t="s" s="2">
-        <v>654</v>
-      </c>
-      <c r="B141" t="s" s="2">
-        <v>654</v>
-      </c>
-      <c r="C141" s="2"/>
-      <c r="D141" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="E141" s="2"/>
-      <c r="F141" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G141" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="H141" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I141" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J141" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="K141" t="s" s="2">
-        <v>655</v>
-      </c>
-      <c r="L141" t="s" s="2">
-        <v>656</v>
-      </c>
-      <c r="M141" t="s" s="2">
-        <v>368</v>
-      </c>
-      <c r="N141" t="s" s="2">
-        <v>657</v>
-      </c>
-      <c r="O141" t="s" s="2">
-        <v>370</v>
-      </c>
-      <c r="P141" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q141" s="2"/>
-      <c r="R141" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S141" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T141" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U141" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V141" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W141" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X141" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y141" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z141" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA141" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB141" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC141" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD141" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE141" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF141" t="s" s="2">
-        <v>654</v>
-      </c>
-      <c r="AG141" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH141" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AI141" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ141" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AK141" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL141" t="s" s="2">
-        <v>658</v>
-      </c>
-      <c r="AM141" t="s" s="2">
-        <v>373</v>
-      </c>
-      <c r="AN141" t="s" s="2">
-        <v>374</v>
-      </c>
-      <c r="AO141" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP141" t="s" s="2">
-        <v>375</v>
-      </c>
-    </row>
-    <row r="142" hidden="true">
-      <c r="A142" t="s" s="2">
-        <v>659</v>
-      </c>
-      <c r="B142" t="s" s="2">
-        <v>659</v>
-      </c>
-      <c r="C142" s="2"/>
-      <c r="D142" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="E142" s="2"/>
-      <c r="F142" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G142" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="H142" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I142" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J142" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="K142" t="s" s="2">
-        <v>191</v>
-      </c>
-      <c r="L142" t="s" s="2">
-        <v>660</v>
-      </c>
-      <c r="M142" t="s" s="2">
-        <v>661</v>
-      </c>
-      <c r="N142" t="s" s="2">
-        <v>662</v>
-      </c>
-      <c r="O142" t="s" s="2">
-        <v>424</v>
-      </c>
-      <c r="P142" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q142" s="2"/>
-      <c r="R142" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S142" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T142" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U142" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V142" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W142" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X142" t="s" s="2">
-        <v>425</v>
-      </c>
-      <c r="Y142" t="s" s="2">
-        <v>426</v>
-      </c>
-      <c r="Z142" t="s" s="2">
-        <v>427</v>
-      </c>
-      <c r="AA142" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB142" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC142" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD142" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE142" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF142" t="s" s="2">
-        <v>659</v>
-      </c>
-      <c r="AG142" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH142" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AI142" t="s" s="2">
-        <v>428</v>
-      </c>
-      <c r="AJ142" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AK142" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL142" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM142" t="s" s="2">
-        <v>136</v>
-      </c>
-      <c r="AN142" t="s" s="2">
-        <v>429</v>
-      </c>
-      <c r="AO142" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP142" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="143" hidden="true">
-      <c r="A143" t="s" s="2">
-        <v>663</v>
-      </c>
-      <c r="B143" t="s" s="2">
-        <v>663</v>
-      </c>
-      <c r="C143" s="2"/>
-      <c r="D143" t="s" s="2">
-        <v>431</v>
-      </c>
-      <c r="E143" s="2"/>
-      <c r="F143" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G143" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H143" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I143" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J143" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="K143" t="s" s="2">
-        <v>191</v>
-      </c>
-      <c r="L143" t="s" s="2">
-        <v>432</v>
-      </c>
-      <c r="M143" t="s" s="2">
-        <v>433</v>
-      </c>
-      <c r="N143" t="s" s="2">
-        <v>434</v>
-      </c>
-      <c r="O143" t="s" s="2">
-        <v>435</v>
-      </c>
-      <c r="P143" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q143" s="2"/>
-      <c r="R143" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S143" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T143" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U143" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V143" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W143" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X143" t="s" s="2">
-        <v>425</v>
-      </c>
-      <c r="Y143" t="s" s="2">
-        <v>436</v>
-      </c>
-      <c r="Z143" t="s" s="2">
-        <v>437</v>
-      </c>
-      <c r="AA143" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB143" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC143" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD143" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE143" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF143" t="s" s="2">
-        <v>663</v>
-      </c>
-      <c r="AG143" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH143" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI143" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ143" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AK143" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL143" t="s" s="2">
-        <v>438</v>
-      </c>
-      <c r="AM143" t="s" s="2">
-        <v>439</v>
-      </c>
-      <c r="AN143" t="s" s="2">
-        <v>440</v>
-      </c>
-      <c r="AO143" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP143" t="s" s="2">
-        <v>441</v>
-      </c>
-    </row>
-    <row r="144" hidden="true">
-      <c r="A144" t="s" s="2">
-        <v>664</v>
-      </c>
-      <c r="B144" t="s" s="2">
-        <v>664</v>
-      </c>
-      <c r="C144" s="2"/>
-      <c r="D144" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="E144" s="2"/>
-      <c r="F144" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G144" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H144" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I144" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J144" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="K144" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="L144" t="s" s="2">
-        <v>665</v>
-      </c>
-      <c r="M144" t="s" s="2">
-        <v>666</v>
-      </c>
-      <c r="N144" t="s" s="2">
-        <v>491</v>
-      </c>
-      <c r="O144" t="s" s="2">
-        <v>492</v>
-      </c>
-      <c r="P144" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q144" s="2"/>
-      <c r="R144" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S144" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T144" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U144" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V144" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W144" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X144" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y144" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z144" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA144" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB144" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC144" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD144" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE144" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF144" t="s" s="2">
-        <v>664</v>
-      </c>
-      <c r="AG144" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH144" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI144" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ144" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AK144" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL144" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM144" t="s" s="2">
-        <v>497</v>
-      </c>
-      <c r="AN144" t="s" s="2">
-        <v>498</v>
-      </c>
-      <c r="AO144" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP144" t="s" s="2">
         <v>82</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AP144">
+  <autoFilter ref="A1:AP106">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -19833,7 +15094,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI143">
+  <conditionalFormatting sqref="A2:AI105">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>
